--- a/hasil_prediksi_skipgram_naive_bayes.xlsx
+++ b/hasil_prediksi_skipgram_naive_bayes.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -490,11 +490,11 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Benar</t>
+          <t>Salah</t>
         </is>
       </c>
     </row>
@@ -519,10 +519,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -551,14 +551,14 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Benar</t>
+          <t>Salah</t>
         </is>
       </c>
     </row>
@@ -599,10 +599,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -647,14 +647,14 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Benar</t>
+          <t>Salah</t>
         </is>
       </c>
     </row>
@@ -666,11 +666,11 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Salah</t>
+          <t>Benar</t>
         </is>
       </c>
     </row>
@@ -679,10 +679,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -695,10 +695,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -714,11 +714,11 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Salah</t>
+          <t>Benar</t>
         </is>
       </c>
     </row>
@@ -727,10 +727,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -743,10 +743,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -855,10 +855,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -871,10 +871,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -903,14 +903,14 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Salah</t>
+          <t>Benar</t>
         </is>
       </c>
     </row>
@@ -935,10 +935,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/hasil_prediksi_skipgram_naive_bayes.xlsx
+++ b/hasil_prediksi_skipgram_naive_bayes.xlsx
@@ -650,11 +650,11 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Salah</t>
+          <t>Benar</t>
         </is>
       </c>
     </row>
